--- a/dataset/pendaftaran_umum.xlsx
+++ b/dataset/pendaftaran_umum.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1800" yWindow="1860" windowWidth="32400" windowHeight="19180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -25,12 +25,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -45,10 +51,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -444,19 +455,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" outlineLevelCol="0"/>
   <cols>
     <col width="17.5" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
-    <col width="12.6640625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.5" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
-    <col width="10.5" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="12.1640625" customWidth="1" min="5" max="5"/>
-    <col width="14.33203125" customWidth="1" min="6" max="6"/>
+    <col width="22.83203125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="34.83203125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="11.5" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
+    <col width="10.5" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="12.6640625" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
     <col width="17.5" customWidth="1" style="1" min="7" max="7"/>
     <col width="10.5" customWidth="1" min="8" max="8"/>
     <col width="10.83203125" customWidth="1" style="1" min="9" max="9"/>
@@ -479,26 +490,26 @@
           <t>nama_lengkap</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>tgl_lahir</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>no_whatsapp</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>tgl_pemeriksaan</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>nik_wali</t>
@@ -559,311 +570,301 @@
           <t>domisili</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+    <row r="2" customFormat="1" s="4">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>3509053001929991</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Bambang</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>1980-10-01</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Laki-laki</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" s="3" t="n">
         <v>8123456789</v>
       </c>
-      <c r="F2" t="n">
-        <v>26</v>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>3512052205820001</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>KUSYONO</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>1982-05-22</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>Laki-laki</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="4" t="n">
         <v>81234567890</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>Belum Menikah</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>Pegawai Swasta</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>Kab. Situbondo</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>Kendit</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>Balung</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>Jl. ABCD</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+    </row>
+    <row r="3" customFormat="1" s="4">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>3512345598191001</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Yuni</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>1990-12-01</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>8123456789</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>3512052205820001</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>KUSYONO</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>1982-05-22</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Laki-laki</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>81234567890</v>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Belum Menikah</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Pegawai Swasta</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>Kendit</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>Balung</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>Jl. ABCD</t>
+        </is>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+    <row r="4" ht="17" customFormat="1" customHeight="1" s="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>3512345598191001</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Yuni</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>1990-12-01</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Dwiki Aria</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Laki-laki</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>8123456789</v>
       </c>
-      <c r="F3" t="n">
-        <v>26</v>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>3512052205820001</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>KUSYONO</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>1982-05-22</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Laki-laki</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" s="4" t="n">
         <v>81234567890</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Belum Menikah</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Pegawai Swasta</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Kab. Situbondo</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>Kendit</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Balung</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>Jl. ABCD</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>3512345598191001</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Dwiki Aria</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>8123456789</v>
-      </c>
-      <c r="F4" t="n">
-        <v>16</v>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>3512052205820001</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>KUSYONO</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>1982-05-22</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>81234567890</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Belum Menikah</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Pegawai Swasta</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Jawa Timur</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Kab. Situbondo</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Kendit</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Balung</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Jl. ABCD</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>3321086006890001</t>
+          <t>3512075610720001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>siti sholikhah</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>1989-06-20</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>85231961508</v>
-      </c>
-      <c r="F5" t="n">
-        <v>17</v>
+          <t>Farah Andriani</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>1972-10-16</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>85231961508</t>
+        </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
@@ -912,52 +913,49 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Situbondo</t>
+          <t>Panarukan</t>
         </is>
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>Patokan</t>
+          <t>Sumberkolak</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Puri Pratama</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>Sumberkolak</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>3504016208800001</t>
+          <t>3321086006890001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Siti Nurhamida</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>1980-08-22</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+          <t>siti sholikhah</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>1989-06-20</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>85231961508</v>
       </c>
-      <c r="F6" t="n">
-        <v>18</v>
-      </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
           <t>3509116303960002</t>
@@ -1015,42 +1013,39 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Jl. Kenanga</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>Puri Pratama</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>3512086108860001</t>
+          <t>3504016208800001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alifa Wulandari</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>1986-08-21</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
+          <t>Siti Nurhamida</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>1980-08-22</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>85231961508</v>
       </c>
-      <c r="F7" t="n">
-        <v>18</v>
-      </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
           <t>3509116303960002</t>
@@ -1103,47 +1098,44 @@
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>Dawuhan</t>
+          <t>Patokan</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Dawuhan Parse</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>Jl. Kenanga</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>3512064301860005</t>
+          <t>3512086108860001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amalia</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>1986-01-03</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
+          <t>Alifa Wulandari</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>1986-08-21</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>85231961508</v>
       </c>
-      <c r="F8" t="n">
-        <v>18</v>
-      </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
           <t>3509116303960002</t>
@@ -1196,47 +1188,44 @@
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>Kalibagor</t>
+          <t>Dawuhan</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Kalibagor</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>Dawuhan Parse</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>3512075610720001</t>
+          <t>3512064301860005</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Farah Andriani</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>1972-10-16</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
+          <t>Amalia</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>DUKCAPIL NOTICE</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>1986-01-03</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="n">
         <v>85231961508</v>
       </c>
-      <c r="F9" t="n">
-        <v>18</v>
-      </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
           <t>3509116303960002</t>
@@ -1284,52 +1273,49 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Panarukan</t>
+          <t>Situbondo</t>
         </is>
       </c>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>Sumberkolak</t>
+          <t>Kalibagor</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Sumberkolak</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>Kalibagor</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>3512064901750001</t>
+          <t>3512075610720001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Siti Andayani</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>1975-01-09</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
+          <t>Farah Andriani</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>1972-10-16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="n">
         <v>85231961508</v>
       </c>
-      <c r="F10" t="n">
-        <v>18</v>
-      </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
           <t>3509116303960002</t>
@@ -1377,52 +1363,49 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Situbondo</t>
+          <t>Panarukan</t>
         </is>
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>Kalibagor</t>
+          <t>Sumberkolak</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Kalibagor</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>Sumberkolak</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>3512076709690002</t>
+          <t>3512064901750001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ary Widjajanti</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>1969-09-27</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+          <t>Siti Andayani</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>1975-01-09</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="n">
         <v>85231961508</v>
       </c>
-      <c r="F11" t="n">
-        <v>18</v>
-      </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
           <t>3509116303960002</t>
@@ -1475,47 +1458,44 @@
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>Patokan</t>
+          <t>Kalibagor</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Jl. Anggrek</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>Kalibagor</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>3319091108880005</t>
+          <t>3512076709690002</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Masyudi</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>1988-08-11</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
+          <t>Ary Widjajanti</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>1969-09-27</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="n">
         <v>85231961508</v>
       </c>
-      <c r="F12" t="n">
-        <v>18</v>
-      </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
           <t>3509116303960002</t>
@@ -1553,62 +1533,59 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Jawa Tengah</t>
+          <t>Jawa Timur</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Kab. Kudus</t>
+          <t>Kab. Situbondo</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dawe</t>
+          <t>Situbondo</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Kandangmas</t>
+          <t>Patokan</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Kandang Mas</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>SKIPPED: Pasien ini sudah menerima CKG</t>
+          <t>Jl. Anggrek</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>3512096104830001</t>
+          <t>3319091108880005</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dwi Usriya</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>1983-04-21</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
+          <t>Masyudi</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>1988-08-11</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Laki-laki</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="n">
         <v>85231961508</v>
       </c>
-      <c r="F13" t="n">
-        <v>18</v>
-      </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
           <t>3509116303960002</t>
@@ -1646,62 +1623,59 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Jawa Timur</t>
+          <t>Jawa Tengah</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>Kab. Situbondo</t>
+          <t>Kab. Kudus</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Situbondo</t>
+          <t>Dawe</t>
         </is>
       </c>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>Patokan</t>
+          <t>Kandangmas</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Jl. Anggrek</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>Kandang Mas</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>3512060209800002</t>
+          <t>3512096104830001</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ibnu Haris</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>1980-09-02</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+          <t>Dwi Usriya</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>DUKCAPIL NOTICE</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>1983-04-21</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="n">
         <v>85231961508</v>
       </c>
-      <c r="F14" t="n">
-        <v>18</v>
-      </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
           <t>3509116303960002</t>
@@ -1749,52 +1723,49 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Panarukan</t>
+          <t>Situbondo</t>
         </is>
       </c>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>Perum</t>
+          <t>Patokan</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perum Villa </t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>SKIPPED: Pasien ini sudah menerima CKG</t>
+          <t>Jl. Anggrek</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>3512134301930006</t>
+          <t>3512060209800002</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fitri Ayu Nurjannatin</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>1993-01-03</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
+          <t>Ibnu Haris</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>1980-09-02</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Laki-laki</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="n">
         <v>85231961508</v>
       </c>
-      <c r="F15" t="n">
-        <v>18</v>
-      </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
           <t>3509116303960002</t>
@@ -1842,52 +1813,49 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Asembagus</t>
+          <t>Panarukan</t>
         </is>
       </c>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>Asembagus</t>
+          <t>Perum</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Asembagus</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t xml:space="preserve">Perum Villa </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>3512076508980002</t>
+          <t>3512134301930006</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Maya Sukma Indah Refiana</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>1998-08-25</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
+          <t>Fitri Ayu Nurjannatin</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>1993-01-03</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n">
         <v>85231961508</v>
       </c>
-      <c r="F16" t="n">
-        <v>18</v>
-      </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
           <t>3509116303960002</t>
@@ -1935,52 +1903,49 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Situbondo</t>
+          <t>Asembagus</t>
         </is>
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>Patokan</t>
+          <t>Asembagus</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Jl. Wr Supratman</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>Asembagus</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>3505142311880001</t>
+          <t>3512076508980002</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Untung Slamet Setiawan</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>1988-11-23</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
+          <t>Maya Sukma Indah Refiana</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>1998-08-25</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="n">
         <v>85231961508</v>
       </c>
-      <c r="F17" t="n">
-        <v>18</v>
-      </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
           <t>3509116303960002</t>
@@ -2028,52 +1993,49 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Panarukan</t>
+          <t>Situbondo</t>
         </is>
       </c>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>Sumberkolak</t>
+          <t>Patokan</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Sumberkolak</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>Jl. Wr Supratman</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>3512074106740002</t>
+          <t>3505142311880001</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rofiqa Yuni Astuti</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>1974-06-01</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
+          <t>Untung Slamet Setiawan</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>1988-11-23</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Laki-laki</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n">
         <v>85231961508</v>
       </c>
-      <c r="F18" t="n">
-        <v>18</v>
-      </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
           <t>3509116303960002</t>
@@ -2121,52 +2083,49 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Situbondo</t>
+          <t>Panarukan</t>
         </is>
       </c>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>Patokan</t>
+          <t>Sumberkolak</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Jl. Kenanga</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
+          <t>Sumberkolak</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>3512094206710001</t>
+          <t>3512074106740002</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Yuni Retnowati</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>1971-06-02</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
+          <t>Rofiqa Yuni Astuti</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>1974-06-01</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="n">
         <v>85231961508</v>
       </c>
-      <c r="F19" t="n">
-        <v>18</v>
-      </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
           <t>3509116303960002</t>
@@ -2219,110 +2178,192 @@
       </c>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>Kalibagor</t>
+          <t>Patokan</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Kalibagor</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>SKIPPED: Pasien ini sudah menerima CKG</t>
+          <t>Jl. Kenanga</t>
         </is>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
+          <t>3512094206710001</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Yuni Retnowati</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>1971-06-02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>85231961508</v>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>3509116303960002</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>sri indriyani</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>1996-03-23</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t>85231961508</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Menikah</t>
+        </is>
+      </c>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
+          <t>ASN (Kantor Pemerintah)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="O20" s="1" t="inlineStr">
+        <is>
+          <t>Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Situbondo</t>
+        </is>
+      </c>
+      <c r="Q20" s="1" t="inlineStr">
+        <is>
+          <t>Kalibagor</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Kalibagor</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
           <t>3512081110870001</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Cahyo Murtanto</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>1987-10-11</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Laki-laki</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="F21" s="1" t="n">
         <v>85231961508</v>
       </c>
-      <c r="F20" t="n">
-        <v>18</v>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>3509116303960002</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>sri indriyani</t>
         </is>
       </c>
-      <c r="I20" s="1" t="inlineStr">
+      <c r="I21" s="1" t="inlineStr">
         <is>
           <t>1996-03-23</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>85231961508</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Menikah</t>
         </is>
       </c>
-      <c r="M20" s="1" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>ASN (Kantor Pemerintah)</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="O20" s="1" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Kab. Situbondo</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>Situbondo</t>
         </is>
       </c>
-      <c r="Q20" s="1" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Patokan</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>Jl. Wr Supratman</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
         </is>
       </c>
     </row>

--- a/dataset/pendaftaran_umum.xlsx
+++ b/dataset/pendaftaran_umum.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" outlineLevelCol="0"/>
   <cols>
     <col width="17.5" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="17" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
           <t>3512075610720001</t>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="17" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>3512076709690002</t>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="17" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
           <t>3319091108880005</t>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="17" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
           <t>3512096104830001</t>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="17" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
           <t>3512060209800002</t>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="17" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
           <t>3512134301930006</t>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="17" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
           <t>3512076508980002</t>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="17" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
           <t>3505142311880001</t>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="17" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
           <t>3512074106740002</t>
@@ -2364,6 +2364,1068 @@
       <c r="R21" t="inlineStr">
         <is>
           <t>Jl. Wr Supratman</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>3512072706060001</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DIYO SAPUTRA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>2006-06-27</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Laki-laki</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>85231961508</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>3509116303960002</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>sri indriyani</t>
+        </is>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>1996-03-23</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>85231961508</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Menikah</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>ASN (Kantor Pemerintah)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Panarukan</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Sumberkolak</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Sumberkolak</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>3512071107880001</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>IRWAN EFENDI</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>1988-07-11</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Laki-laki</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>85231961508</v>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>3509116303960002</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>sri indriyani</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>1996-03-23</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>85231961508</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Menikah</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>ASN (Kantor Pemerintah)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Situbondo</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Patokan</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Puri Pratama</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>3512074907990007</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HOLISATUR ROHMAH</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>1999-07-09</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>85231961508</v>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>3509116303960002</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>sri indriyani</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>1996-03-23</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>85231961508</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Menikah</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>ASN (Kantor Pemerintah)</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Situbondo</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Patokan</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Jl. Kenanga</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>3512075906690001</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SITI FATIMAH</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>1969-06-19</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>85231961508</v>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>3509116303960002</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>sri indriyani</t>
+        </is>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>1996-03-23</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>85231961508</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Menikah</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>ASN (Kantor Pemerintah)</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Situbondo</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Dawuhan</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Dawuhan Parse</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>3512070107780010</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MISTARI</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>1978-07-01</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Laki-laki</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>85231961508</v>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>3509116303960002</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>sri indriyani</t>
+        </is>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>1996-03-23</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>85231961508</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Menikah</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>ASN (Kantor Pemerintah)</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Situbondo</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Kalibagor</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Kalibagor</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>3512076006850003</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SUNI YULIANI</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>1988-02-01</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Laki-laki</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>85231961508</v>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>3509116303960002</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>sri indriyani</t>
+        </is>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>1996-03-23</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>85231961508</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Menikah</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>ASN (Kantor Pemerintah)</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Panarukan</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Sumberkolak</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Sumberkolak</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>3512071102790001</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ABU BAKAR</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>1979-02-11</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Laki-laki</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>85231961508</v>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>3509116303960002</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>sri indriyani</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>1996-03-23</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>85231961508</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Menikah</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>ASN (Kantor Pemerintah)</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Situbondo</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Kalibagor</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Kalibagor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>3512075001770008</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TUMIYATI</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Pasien ini sudah menerima CKG</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>1977-01-10</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>85231961508</v>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>3509116303960002</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>sri indriyani</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>1996-03-23</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>85231961508</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Menikah</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>ASN (Kantor Pemerintah)</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Situbondo</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Patokan</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Jl. Anggrek</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>3512075702820002</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SUHAINA</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>1982-02-17</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>85231961508</v>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>3509116303960002</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>sri indriyani</t>
+        </is>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>1996-03-23</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>85231961508</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Menikah</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>ASN (Kantor Pemerintah)</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Jawa Tengah</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Situbondo</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Patokan</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Kandang Mas</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>3512075204810005</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>UCIK BING SLAMET</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>1981-04-01</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>85231961508</v>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>3509116303960002</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>sri indriyani</t>
+        </is>
+      </c>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>1996-03-23</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>85231961508</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Menikah</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>ASN (Kantor Pemerintah)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Situbondo</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Patokan</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Jl. Anggrek</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>3512070107680003</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MISYADI</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>1968-07-01</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Laki-laki</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>85231961508</v>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>3509116303960002</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>sri indriyani</t>
+        </is>
+      </c>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>1996-03-23</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>85231961508</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Menikah</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>ASN (Kantor Pemerintah)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Panarukan</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Perum</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perum Villa </t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>3512074301840005</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SUSANTI</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>1984-01-03</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>85231961508</v>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>3509116303960002</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>sri indriyani</t>
+        </is>
+      </c>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>1996-03-23</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Perempuan</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>85231961508</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Menikah</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>ASN (Kantor Pemerintah)</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Asembagus</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Asembagus</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Asembagus</t>
         </is>
       </c>
     </row>

--- a/dataset/pendaftaran_umum.xlsx
+++ b/dataset/pendaftaran_umum.xlsx
@@ -848,10 +848,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAILED: Locator.click: Timeout 30000ms exceeded.
-Call log:
-  - waiting for get_by_role("button", name="Tutup")
-</t>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -1035,10 +1032,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAILED: Locator.click: Timeout 30000ms exceeded.
-Call log:
-  - waiting for get_by_role("button", name="Tutup")
-</t>
+          <t>SUCCESS</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">

--- a/dataset/pendaftaran_umum.xlsx
+++ b/dataset/pendaftaran_umum.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbokprom12021/PycharmProjects/CKG-Helper/dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DF0B8D-39C2-5C44-9219-4EA25C1FEA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380BE562-6678-E14E-85C9-3567CD833F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -214,18 +214,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -561,7 +556,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" style="1" bestFit="1" customWidth="1"/>
@@ -638,288 +633,248 @@
       </c>
     </row>
     <row r="2" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="1">
         <v>8123456789</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2">
         <v>81234567890</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="Q2" t="s">
         <v>31</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="1">
         <v>8123456789</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3">
         <v>81234567890</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" t="s">
         <v>29</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="Q3" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="R3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:18" s="3" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="1">
         <v>8123456789</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4">
         <v>81234567890</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" t="s">
         <v>30</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="Q4" t="s">
         <v>31</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="R4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" t="s">
         <v>44</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" t="s">
         <v>47</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="N5" t="s">
         <v>28</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="P5" t="s">
         <v>49</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="R5" s="5" t="s">
+      <c r="R5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="5"/>
+      <c r="K6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="5"/>
+      <c r="C7" s="2"/>
+      <c r="K7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="5"/>
+      <c r="C8" s="2"/>
+      <c r="K8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="Q8" s="1"/>
     </row>
     <row r="9" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="2"/>
@@ -1007,6 +962,66 @@
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
     </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33"/>
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34"/>
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35"/>
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36"/>
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37"/>
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38"/>
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39"/>
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40"/>
+      <c r="D40"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41"/>
+      <c r="D41"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42"/>
+      <c r="D42"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43"/>
+      <c r="D43"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44"/>
+      <c r="D44"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45"/>
+      <c r="D45"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46"/>
+      <c r="D46"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47"/>
+      <c r="D47"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/dataset/pendaftaran_umum.xlsx
+++ b/dataset/pendaftaran_umum.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R62"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
   <cols>
     <col width="17.5" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1011,6 +1011,15 @@
       <c r="O18" s="1" t="n"/>
       <c r="Q18" s="1" t="n"/>
     </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28" ht="17" customHeight="1">
       <c r="C28" s="2" t="n"/>
     </row>
@@ -1029,666 +1038,6 @@
       <c r="L32" s="1" t="n"/>
       <c r="M32" s="1" t="n"/>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>3512340601117216</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Muhammad Gilang Ardianto</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2011-01-06</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>3512816207098932</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Carla</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2009-07-22</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>3512321508103429</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Danu Pradipta</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2010-08-15</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>3512625201111915</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Pia Rahayu Hariyah</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2011-01-12</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>3512613101107732</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Jindra Mardhiyah</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2010-01-31</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>3512426506108403</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Diana Kuswandari</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2010-06-25</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>3512784101137725</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Hasna Yuni Ramadan</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2013-01-01</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>3512235009168538</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Cindy</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2016-09-10</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>3512294306166752</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Maida</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2016-06-03</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>3512786908099916</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Devi</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2009-08-29</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>3512024903105211</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Ayu Kurnia Wibisono</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2010-03-09</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>3512534309125834</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Febi Ani Prabowo</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2012-09-03</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>3512182504110532</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Nasrullah</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2011-04-25</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>3512751011123761</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Ajimin Melani</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2012-11-10</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>3512961009096522</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Utama Permadi</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2009-09-10</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>3512804205145054</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Zizi Suartini</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2014-05-02</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>3512475210138683</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Elma Hutagalung</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2013-10-12</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>3512035902122420</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Dian</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2012-02-19</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>3512931112105764</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Raditya Ridwan Yuliarti</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2010-12-11</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>3512652411137642</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Gading Lukman Usamah</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2013-11-24</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>3512261111150528</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Liman Irawan</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2015-11-11</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>3512305909107734</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Carla Halimah Santoso</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2010-09-19</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>3512520506121671</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Lukita Sihombing</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2012-06-05</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>3512285508159903</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Restu</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2015-08-15</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>3512666409168063</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Alika Siska Wijayanti</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2016-09-24</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>3512170309150367</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Lamar Nanda Uyainah</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2015-09-03</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>3512994504093839</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Malika Lestari</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2009-04-05</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>3512746008151731</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Oni Anggriawan</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2015-08-20</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Perempuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>3512892011165919</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Olga Habibi</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2016-11-20</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>3512732104116505</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Saka</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2011-04-21</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Laki-laki</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
